--- a/Herman_sim/bachelor_montecarlo/model_mc_ready_6.xlsx
+++ b/Herman_sim/bachelor_montecarlo/model_mc_ready_6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studntnu-my.sharepoint.com/personal/hermaose_ntnu_no/Documents/Programmering Bachelor/Transport-under-usikkerhet---Monte-Carlo/Herman_sim/bachelor_montecarlo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{5AC497FB-2049-4AA6-91D9-3C030F7F39D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F46D3B43-16B5-42AC-9380-9656F72BB102}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{5AC497FB-2049-4AA6-91D9-3C030F7F39D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5FB9BDF-DB58-4CA6-A5F7-9F58D77338EE}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ruter" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="181">
   <si>
     <t>RuteID</t>
   </si>
@@ -225,27 +228,15 @@
     <t>VFTTS (kr/time)</t>
   </si>
   <si>
-    <t>Kilde: De Jong et al. (2004/2007); 30-50 EUR/time for veitransport (konservativt estimat)</t>
-  </si>
-  <si>
     <t>Rail kostnad pr tonn-km</t>
   </si>
   <si>
-    <t>Kilde: EU RECORDIT (2003); typisk 0.04-0.10 EUR/tonn-km for intermodal Europa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sjø kostnad pr kilometer - RoRo </t>
   </si>
   <si>
-    <t>UNCTAD (2023); RoRo-bransje 5-10 kr/km, midtpunkt valgt"</t>
-  </si>
-  <si>
     <t>Vei kostnad pr tonn-km</t>
   </si>
   <si>
-    <t>Kilde: IRU/Upply Q4 2024 ~€1.20/km ÷ 24t = 0.583 kr/tonn-km</t>
-  </si>
-  <si>
     <t>Slovenia</t>
   </si>
   <si>
@@ -261,9 +252,6 @@
     <t>Lastemengde (tonn/trailer)</t>
   </si>
   <si>
-    <t>Kilde: Hydro (e-post, høst 2024); 24-25 tonn avh. av land</t>
-  </si>
-  <si>
     <t xml:space="preserve">Koper </t>
   </si>
   <si>
@@ -598,9 +586,6 @@
   </si>
   <si>
     <t xml:space="preserve">  Brukes til å verdsette redusert ledetidsvariabilitet (Andersson et al. 2017).</t>
-  </si>
-  <si>
-    <t>Hva må til for at sjø skal bli best</t>
   </si>
 </sst>
 </file>
@@ -608,11 +593,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-&quot;kr&quot;\ * #,##0.00_-;\-&quot;kr&quot;\ * #,##0.00_-;_-&quot;kr&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;kr &quot;* #,##0.00_-;&quot;-kr &quot;* #,##0.00_-;_-&quot;kr &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;kr &quot;* #,##0.00_-;&quot;-kr &quot;* #,##0.00_-;_-&quot;kr &quot;* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,7 +826,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -857,28 +842,28 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
@@ -894,7 +879,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1331,7 +1316,7 @@
                 <c:pt idx="4">
                   <c:v>149028.71428571426</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="_(&quot;kr&quot;* #,##0.00_);_(&quot;kr&quot;* \(#,##0.00\);_(&quot;kr&quot;* &quot;-&quot;??_);_(@_)">
+                <c:pt idx="5" formatCode="_-&quot;kr&quot;\ * #\ ##0.00_-;\-&quot;kr&quot;\ * #\ ##0.00_-;_-&quot;kr&quot;\ * &quot;-&quot;??_-;_-@_-">
                   <c:v>88388.112903225803</c:v>
                 </c:pt>
               </c:numCache>
@@ -2746,24 +2731,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R49"/>
-  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
-    <col min="3" max="4" width="19.86328125" customWidth="1"/>
-    <col min="5" max="5" width="14.46484375" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" customWidth="1"/>
-    <col min="7" max="7" width="18.46484375" customWidth="1"/>
-    <col min="8" max="8" width="19.3984375" customWidth="1"/>
+    <col min="2" max="2" width="10.375" customWidth="1"/>
+    <col min="3" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="19.375" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="11.9296875" customWidth="1"/>
-    <col min="13" max="13" width="11.73046875" customWidth="1"/>
-    <col min="14" max="14" width="11.86328125" customWidth="1"/>
+    <col min="12" max="12" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="11.75" customWidth="1"/>
+    <col min="14" max="14" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" ht="14.25" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2819,7 +2804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:18" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2873,7 +2858,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18" ht="14.25" customHeight="1">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2927,7 +2912,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="14.25" customHeight="1">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2981,7 +2966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" ht="14.25" customHeight="1">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3035,7 +3020,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" ht="14.25" customHeight="1">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -3089,7 +3074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" ht="14.25" customHeight="1">
       <c r="B7" s="14" t="s">
         <v>34</v>
       </c>
@@ -3139,7 +3124,7 @@
         <v>7.5975198412698424</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" ht="14.25" customHeight="1">
       <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
@@ -3189,7 +3174,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18" ht="14.25" customHeight="1">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -3243,7 +3228,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18" ht="14.25" customHeight="1">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -3297,7 +3282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" ht="14.25" customHeight="1">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -3351,7 +3336,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" ht="14.25" customHeight="1">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -3405,7 +3390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:18" ht="14.25" customHeight="1">
       <c r="B15" s="18" t="s">
         <v>34</v>
       </c>
@@ -3455,19 +3440,19 @@
         <v>7.1937500000000014</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:18" ht="14.25" customHeight="1">
       <c r="J16" s="21"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:18" ht="14.25" customHeight="1">
       <c r="J17" s="21"/>
       <c r="M17" s="21"/>
     </row>
-    <row r="18" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:18" ht="14.25" customHeight="1">
       <c r="J18" s="21"/>
       <c r="M18" s="21"/>
     </row>
-    <row r="21" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:18" ht="14.25" customHeight="1">
       <c r="B21" s="5" t="s">
         <v>42</v>
       </c>
@@ -3517,7 +3502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:18" ht="14.25" customHeight="1">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -3569,7 +3554,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:18" ht="14.25" customHeight="1">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -3621,7 +3606,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:18" ht="14.25" customHeight="1">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3673,7 +3658,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:18" ht="14.25" customHeight="1">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -3725,7 +3710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:18" ht="14.25" customHeight="1">
       <c r="B26" s="14" t="s">
         <v>34</v>
       </c>
@@ -3772,7 +3757,7 @@
         <v>8.7304563492063494</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:18" ht="14.25" customHeight="1">
       <c r="B31" s="6" t="s">
         <v>46</v>
       </c>
@@ -3822,7 +3807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:18" ht="14.25" customHeight="1">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -3874,7 +3859,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:18" ht="14.25" customHeight="1">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -3926,7 +3911,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:18" ht="14.25" customHeight="1">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -3978,7 +3963,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:18" ht="14.25" customHeight="1">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -4030,7 +4015,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:18" ht="14.25" customHeight="1">
       <c r="B36" s="14" t="s">
         <v>34</v>
       </c>
@@ -4077,7 +4062,7 @@
         <v>7.3971230158730163</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:18" ht="14.25" customHeight="1">
       <c r="B39" s="6" t="s">
         <v>49</v>
       </c>
@@ -4127,7 +4112,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:18" ht="14.25" customHeight="1">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -4181,7 +4166,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:18" ht="14.25" customHeight="1">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -4235,7 +4220,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:18" ht="14.25" customHeight="1">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -4289,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:18" ht="14.25" customHeight="1">
       <c r="B43" s="14" t="s">
         <v>34</v>
       </c>
@@ -4339,7 +4324,7 @@
         <v>12.182034632034631</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:18" ht="14.25" customHeight="1">
       <c r="B46" s="6" t="s">
         <v>52</v>
       </c>
@@ -4389,7 +4374,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:18" ht="14.25" customHeight="1">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -4443,7 +4428,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:18" ht="14.25" customHeight="1">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -4497,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:17" ht="14.25" customHeight="1">
       <c r="B49" s="24" t="s">
         <v>34</v>
       </c>
@@ -4556,20 +4541,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P50"/>
-  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" customWidth="1"/>
-    <col min="3" max="3" width="45.06640625" customWidth="1"/>
+    <col min="1" max="1" width="29.375" customWidth="1"/>
+    <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="45.125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1328125" customWidth="1"/>
-    <col min="14" max="14" width="16.1328125" customWidth="1"/>
-    <col min="15" max="15" width="10.265625" customWidth="1"/>
-    <col min="16" max="16" width="20.19921875" customWidth="1"/>
+    <col min="12" max="12" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.125" customWidth="1"/>
+    <col min="14" max="14" width="16.125" customWidth="1"/>
+    <col min="15" max="15" width="10.25" customWidth="1"/>
+    <col min="16" max="16" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" ht="14.25" customHeight="1">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -4607,15 +4592,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="27">
         <v>330</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6">
@@ -4641,15 +4623,12 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
     </row>
-    <row r="3" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="27">
         <v>0.5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6">
@@ -4675,15 +4654,12 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6">
@@ -4709,15 +4685,12 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B5" s="27">
         <v>0.75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6">
@@ -4733,7 +4706,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M5" s="7">
         <f>$B$3*Ruter!H5*$B$9</f>
@@ -4743,9 +4716,9 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B6">
         <v>1000</v>
@@ -4761,7 +4734,7 @@
         <v>32</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>33</v>
@@ -4774,9 +4747,9 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="14.25" customHeight="1">
       <c r="A7" s="28" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B7" s="28">
         <v>0</v>
@@ -4806,26 +4779,23 @@
         <v>96923.357142857159</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="14.25" customHeight="1">
       <c r="A8" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B8" s="28">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="14.25" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B9" s="27">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:16" ht="14.25" customHeight="1">
       <c r="G10" s="5" t="s">
         <v>35</v>
       </c>
@@ -4857,7 +4827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="14.25" customHeight="1">
       <c r="G11" s="6"/>
       <c r="H11" s="6">
         <v>1</v>
@@ -4882,13 +4852,7 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
     </row>
-    <row r="12" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12">
-        <v>0.2</v>
-      </c>
-      <c r="C12">
-        <v>0.6</v>
-      </c>
+    <row r="12" spans="1:16" ht="14.25" customHeight="1">
       <c r="G12" s="6"/>
       <c r="H12" s="6">
         <v>2</v>
@@ -4913,7 +4877,7 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
     </row>
-    <row r="13" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" ht="14.25" customHeight="1">
       <c r="G13" s="6"/>
       <c r="H13" s="6">
         <v>3</v>
@@ -4938,10 +4902,7 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
     </row>
-    <row r="14" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C14" t="s">
-        <v>186</v>
-      </c>
+    <row r="14" spans="1:16" ht="14.25" customHeight="1">
       <c r="G14" s="6"/>
       <c r="H14" s="6">
         <v>4</v>
@@ -4966,7 +4927,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
-    <row r="15" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" ht="14.25" customHeight="1">
       <c r="G15" s="30" t="s">
         <v>34</v>
       </c>
@@ -4992,14 +4953,14 @@
         <v>85751.500000000015</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" ht="14.25" customHeight="1">
       <c r="P16" s="32"/>
     </row>
-    <row r="17" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="18" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="7:16" ht="14.25" customHeight="1"/>
+    <row r="18" spans="7:16" ht="14.25" customHeight="1">
       <c r="P18" s="32"/>
     </row>
-    <row r="21" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="7:16" ht="14.25" customHeight="1">
       <c r="G21" s="5" t="s">
         <v>42</v>
       </c>
@@ -5031,7 +4992,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="7:16" ht="14.25" customHeight="1">
       <c r="G22" s="6"/>
       <c r="H22" s="6">
         <v>1</v>
@@ -5054,7 +5015,7 @@
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
     </row>
-    <row r="23" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="7:16" ht="14.25" customHeight="1">
       <c r="G23" s="6"/>
       <c r="H23" s="6">
         <v>2</v>
@@ -5077,7 +5038,7 @@
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
-    <row r="24" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="7:16" ht="14.25" customHeight="1">
       <c r="G24" s="6"/>
       <c r="H24" s="6">
         <v>3</v>
@@ -5100,7 +5061,7 @@
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
     </row>
-    <row r="25" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="7:16" ht="14.25" customHeight="1">
       <c r="G25" s="6"/>
       <c r="H25" s="6">
         <v>4</v>
@@ -5123,7 +5084,7 @@
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
     </row>
-    <row r="26" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="7:16" ht="14.25" customHeight="1">
       <c r="G26" s="23" t="s">
         <v>34</v>
       </c>
@@ -5149,10 +5110,10 @@
         <v>98574.21428571429</v>
       </c>
     </row>
-    <row r="27" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="7:16" ht="14.25" customHeight="1">
       <c r="P27" s="32"/>
     </row>
-    <row r="30" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="7:16" ht="14.25" customHeight="1">
       <c r="G30" s="6" t="s">
         <v>46</v>
       </c>
@@ -5184,7 +5145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="7:16" ht="14.25" customHeight="1">
       <c r="G31" s="6"/>
       <c r="H31" s="6">
         <v>1</v>
@@ -5207,7 +5168,7 @@
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
     </row>
-    <row r="32" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="7:16" ht="14.25" customHeight="1">
       <c r="G32" s="6"/>
       <c r="H32" s="6">
         <v>2</v>
@@ -5230,7 +5191,7 @@
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
-    <row r="33" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="7:16" ht="14.25" customHeight="1">
       <c r="G33" s="6"/>
       <c r="H33" s="6">
         <v>3</v>
@@ -5253,7 +5214,7 @@
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
     </row>
-    <row r="34" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="7:16" ht="14.25" customHeight="1">
       <c r="G34" s="6"/>
       <c r="H34" s="6">
         <v>4</v>
@@ -5263,7 +5224,7 @@
         <v>39</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>33</v>
@@ -5276,7 +5237,7 @@
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
     </row>
-    <row r="35" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="7:16" ht="14.25" customHeight="1">
       <c r="G35" s="23" t="s">
         <v>34</v>
       </c>
@@ -5302,10 +5263,10 @@
         <v>91974.21428571429</v>
       </c>
     </row>
-    <row r="36" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="7:16" ht="14.25" customHeight="1">
       <c r="P36" s="32"/>
     </row>
-    <row r="39" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="7:16" ht="14.25" customHeight="1">
       <c r="G39" s="7" t="s">
         <v>49</v>
       </c>
@@ -5337,7 +5298,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="7:16" ht="14.25" customHeight="1">
       <c r="G40" s="7"/>
       <c r="H40" s="7">
         <v>1</v>
@@ -5362,7 +5323,7 @@
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
     </row>
-    <row r="41" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="7:16" ht="14.25" customHeight="1">
       <c r="G41" s="7"/>
       <c r="H41" s="7">
         <v>2</v>
@@ -5387,7 +5348,7 @@
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
     </row>
-    <row r="42" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="7:16" ht="14.25" customHeight="1">
       <c r="G42" s="7"/>
       <c r="H42" s="7">
         <v>3</v>
@@ -5412,7 +5373,7 @@
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
     </row>
-    <row r="43" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="7:16" ht="14.25" customHeight="1">
       <c r="G43" s="20" t="s">
         <v>34</v>
       </c>
@@ -5438,7 +5399,7 @@
         <v>149028.71428571426</v>
       </c>
     </row>
-    <row r="47" spans="7:16" x14ac:dyDescent="0.45">
+    <row r="47" spans="7:16">
       <c r="G47" s="7" t="s">
         <v>52</v>
       </c>
@@ -5470,7 +5431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="7:16" x14ac:dyDescent="0.45">
+    <row r="48" spans="7:16">
       <c r="G48" s="7"/>
       <c r="H48" s="7">
         <v>1</v>
@@ -5495,7 +5456,7 @@
       <c r="O48" s="7"/>
       <c r="P48" s="7"/>
     </row>
-    <row r="49" spans="7:16" x14ac:dyDescent="0.45">
+    <row r="49" spans="7:16">
       <c r="G49" s="7"/>
       <c r="H49" s="7">
         <v>2</v>
@@ -5520,7 +5481,7 @@
       <c r="O49" s="7"/>
       <c r="P49" s="7"/>
     </row>
-    <row r="50" spans="7:16" x14ac:dyDescent="0.45">
+    <row r="50" spans="7:16">
       <c r="G50" s="20" t="s">
         <v>34</v>
       </c>
@@ -5553,16 +5514,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:D8"/>
-  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="19.53125" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -5571,10 +5532,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.25" customHeight="1">
       <c r="A3" s="33" t="s">
         <v>18</v>
       </c>
@@ -5591,7 +5552,7 @@
         <v>182.34047619047621</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="14.25" customHeight="1">
       <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
@@ -5608,7 +5569,7 @@
         <v>172.65000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="14.25" customHeight="1">
       <c r="A5" s="20" t="s">
         <v>43</v>
       </c>
@@ -5625,7 +5586,7 @@
         <v>209.53095238095239</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="14.25" customHeight="1">
       <c r="A6" s="36" t="s">
         <v>47</v>
       </c>
@@ -5642,7 +5603,7 @@
         <v>177.53095238095239</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="14.25" customHeight="1">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -5659,7 +5620,7 @@
         <v>292.36883116883115</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4">
       <c r="A8" s="45" t="s">
         <v>53</v>
       </c>
@@ -5686,144 +5647,144 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="30.19921875" customWidth="1"/>
+    <col min="2" max="2" width="30.25" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="41" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="17.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="37" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="38" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C6" s="39">
         <v>0.12</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C7" s="39">
         <v>0.15</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="38" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C8" s="39">
         <v>0.2</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="38" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C9" s="39">
         <v>0.08</v>
       </c>
       <c r="D9" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1"/>
+    <row r="11" spans="1:6" ht="15" customHeight="1"/>
+    <row r="12" spans="1:6" ht="15" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A13" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="D13" s="37" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>98</v>
-      </c>
       <c r="E13" s="37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.25" customHeight="1">
       <c r="A14" s="38" t="s">
         <v>20</v>
       </c>
@@ -5837,15 +5798,15 @@
         <v>24</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1">
       <c r="A15" s="38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B15" s="40">
         <v>8</v>
@@ -5857,13 +5818,13 @@
         <v>24</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1">
       <c r="A16" s="38" t="s">
         <v>39</v>
       </c>
@@ -5877,13 +5838,13 @@
         <v>12</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1">
       <c r="A17" s="38" t="s">
         <v>26</v>
       </c>
@@ -5897,39 +5858,39 @@
         <v>8</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1"/>
+    <row r="19" spans="1:6" ht="15" customHeight="1"/>
+    <row r="20" spans="1:6" ht="15" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1">
       <c r="A22" s="37" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1">
       <c r="A23" s="38" t="s">
         <v>20</v>
       </c>
@@ -5937,27 +5898,27 @@
         <v>68</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.25" customHeight="1">
       <c r="A24" s="38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B24" s="40">
         <v>68</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="14.25" customHeight="1">
       <c r="A25" s="38" t="s">
         <v>39</v>
       </c>
@@ -5965,13 +5926,13 @@
         <v>48</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1">
       <c r="A26" s="38" t="s">
         <v>26</v>
       </c>
@@ -5979,42 +5940,42 @@
         <v>0</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="28" spans="1:6" ht="15" customHeight="1"/>
+    <row r="29" spans="1:6" ht="15" customHeight="1">
       <c r="A29" s="10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1">
       <c r="A30" s="41" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1">
       <c r="A31" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B31" s="42">
         <v>0.25</v>
@@ -6026,15 +5987,15 @@
         <v>1</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1">
       <c r="A32" s="38" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B32" s="42">
         <v>0.5</v>
@@ -6046,15 +6007,15 @@
         <v>3</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1">
       <c r="A33" s="38" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B33" s="42">
         <v>1</v>
@@ -6066,15 +6027,15 @@
         <v>3</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B34" s="43">
         <v>3</v>
@@ -6086,15 +6047,15 @@
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1">
       <c r="A35" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B35" s="43">
         <v>0.5</v>
@@ -6106,15 +6067,15 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B36" s="43">
         <v>0.5</v>
@@ -6126,15 +6087,15 @@
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B37" s="43">
         <v>0.25</v>
@@ -6146,15 +6107,15 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1">
       <c r="A38" s="37" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B38" s="43">
         <v>0.25</v>
@@ -6166,15 +6127,15 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1">
       <c r="A39" s="38" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B39" s="42">
         <v>0.25</v>
@@ -6186,15 +6147,15 @@
         <v>1</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" customHeight="1">
       <c r="A40" s="38" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B40" s="42">
         <v>0.5</v>
@@ -6206,13 +6167,13 @@
         <v>3</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" s="38"/>
       <c r="B41" s="40"/>
       <c r="C41" s="40"/>
@@ -6220,7 +6181,7 @@
       <c r="E41" s="40"/>
       <c r="F41" s="38"/>
     </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" ht="15" customHeight="1">
       <c r="A42" s="38"/>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -6228,90 +6189,90 @@
       <c r="E42" s="40"/>
       <c r="F42" s="38"/>
     </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" ht="15" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="27.75" customHeight="1">
       <c r="A46" s="37" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1">
       <c r="A47" s="38" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B47" s="40">
         <v>10000</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1">
       <c r="A48" s="38" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B48" s="40">
         <v>42</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1">
       <c r="A49" s="38" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B49" s="40">
         <v>0</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1"/>
+    <row r="51" spans="1:6" ht="15" customHeight="1"/>
+    <row r="52" spans="1:6" ht="15" customHeight="1"/>
+    <row r="53" spans="1:6" ht="15" customHeight="1"/>
+    <row r="54" spans="1:6" ht="15" customHeight="1"/>
+    <row r="57" spans="1:6" ht="15" customHeight="1"/>
+    <row r="58" spans="1:6" ht="15" customHeight="1"/>
+    <row r="59" spans="1:6" ht="15" customHeight="1"/>
+    <row r="60" spans="1:6" ht="15" customHeight="1">
       <c r="A60" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15" customHeight="1">
       <c r="A61" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="14.25" customHeight="1">
       <c r="A62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="14.25" customHeight="1">
       <c r="A63" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B63" s="43">
         <v>1</v>
@@ -6323,10 +6284,10 @@
         <v>6</v>
       </c>
       <c r="E63" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F63" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -6338,7 +6299,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -6346,167 +6307,167 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="46" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
       <c r="D1" s="46"/>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
       <c r="D2" s="47"/>
     </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="37" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B5" s="40">
         <v>330</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="38" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B6" s="40">
         <v>0.8</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B7" s="40">
         <v>0.5</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="38" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B8" s="40">
         <v>0.75</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="38" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B9" s="40">
         <v>7</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="38" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B10" s="40">
         <v>0</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B11" s="40">
         <v>1000</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="38" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B12" s="40">
         <v>24</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1">
       <c r="A15" s="48" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B15" s="48"/>
       <c r="C15" s="48"/>
       <c r="D15" s="48"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" ht="15" customHeight="1">
       <c r="A16" s="47" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B16" s="47"/>
       <c r="C16" s="47"/>
       <c r="D16" s="47"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" ht="15" customHeight="1">
       <c r="A17" s="47" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B17" s="47"/>
       <c r="C17" s="47"/>
